--- a/BaoCaoThongKe.xlsx
+++ b/BaoCaoThongKe.xlsx
@@ -6,13 +6,60 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Thong Ke Thu Phi" r:id="rId3" sheetId="1"/>
+    <sheet name="Tổng quan &amp; Dân cư" r:id="rId3" sheetId="1"/>
+    <sheet name="Chi tiết các khoản thu" r:id="rId4" sheetId="2"/>
+    <sheet name="Doanh thu theo thời gian" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="24">
+  <si>
+    <t>CHỈ SỐ TỔNG QUAN HỆ THỐNG</t>
+  </si>
+  <si>
+    <t>Chỉ số</t>
+  </si>
+  <si>
+    <t>Giá trị</t>
+  </si>
+  <si>
+    <t>Tổng số cư dân (người)</t>
+  </si>
+  <si>
+    <t>Tổng số căn hộ</t>
+  </si>
+  <si>
+    <t>Tổng doanh thu (VND)</t>
+  </si>
+  <si>
+    <t>Tổng nợ chưa nộp (VND)</t>
+  </si>
+  <si>
+    <t>THỐNG KÊ CƯ DÂN THEO GIỚI TÍNH</t>
+  </si>
+  <si>
+    <t>Giới tính</t>
+  </si>
+  <si>
+    <t>Số lượng</t>
+  </si>
+  <si>
+    <t>NAM</t>
+  </si>
+  <si>
+    <t>NU</t>
+  </si>
+  <si>
+    <t>THỐNG KÊ TÌNH TRẠNG CƯ TRÚ</t>
+  </si>
+  <si>
+    <t>Trạng thái cư trú</t>
+  </si>
+  <si>
+    <t>THUONG_TRU</t>
+  </si>
   <si>
     <t>STT</t>
   </si>
@@ -20,13 +67,25 @@
     <t>Khoản Thu</t>
   </si>
   <si>
-    <t>Tổng Đã Thu (VND)</t>
+    <t>Tổng Đã Nộp (VND)</t>
+  </si>
+  <si>
+    <t>Tổng Chưa Nộp (VND)</t>
+  </si>
+  <si>
+    <t>Quỹ vì người nghèo năm 2023</t>
   </si>
   <si>
     <t>Phí dịch vụ chung cư Tháng 10/2023</t>
   </si>
   <si>
-    <t>Quỹ vì người nghèo năm 2023</t>
+    <t>Mốc thời gian</t>
+  </si>
+  <si>
+    <t>Doanh thu (VND)</t>
+  </si>
+  <si>
+    <t>2023-10</t>
   </si>
 </sst>
 </file>
@@ -34,7 +93,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="5">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
@@ -42,16 +101,46 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="12.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="darkGray"/>
     </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="22"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="22"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -59,57 +148,239 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true"/>
   </cellXfs>
 </styleSheet>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="4.19140625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="33.41796875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="18.12109375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="33.80078125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="9.94140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s" s="0">
+      <c r="A1" t="s" s="4">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="0">
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="1">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="B3" t="s" s="1">
         <v>2</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>728500.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>2772000.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="1">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n" s="2">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="1">
+        <v>13</v>
+      </c>
+      <c r="B17" t="s" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B18" t="n" s="2">
+        <v>3.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="4.2734375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="33.41796875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="18.85546875" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="21.21875" customWidth="true" bestFit="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>17</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>18</v>
+      </c>
+    </row>
     <row r="2">
-      <c r="A2" t="n" s="0">
+      <c r="A2" t="n" s="2">
         <v>1.0</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C2" t="n" s="0">
+      <c r="B2" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="C2" t="n" s="3">
+        <v>200000.0</v>
+      </c>
+      <c r="D2" t="n" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="C3" t="n" s="3">
         <v>528500.0</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n" s="0">
-        <v>2.0</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>4</v>
-      </c>
-      <c r="C3" t="n" s="0">
-        <v>200000.0</v>
+      <c r="D3" t="n" s="3">
+        <v>2772000.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="4.2734375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="13.8046875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="16.69921875" customWidth="true" bestFit="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>21</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="C2" t="n" s="3">
+        <v>728500.0</v>
       </c>
     </row>
   </sheetData>

--- a/BaoCaoThongKe.xlsx
+++ b/BaoCaoThongKe.xlsx
@@ -73,10 +73,10 @@
     <t>Tổng Chưa Nộp (VND)</t>
   </si>
   <si>
+    <t>Phí dịch vụ chung cư Tháng 10/2023</t>
+  </si>
+  <si>
     <t>Quỹ vì người nghèo năm 2023</t>
-  </si>
-  <si>
-    <t>Phí dịch vụ chung cư Tháng 10/2023</t>
   </si>
   <si>
     <t>Mốc thời gian</t>
@@ -190,7 +190,7 @@
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="33.80078125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="9.94140625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="9.35546875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -219,7 +219,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="6">
@@ -235,7 +235,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>2772000.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="10">
@@ -326,7 +326,7 @@
         <v>19</v>
       </c>
       <c r="C2" t="n" s="3">
-        <v>200000.0</v>
+        <v>0.0</v>
       </c>
       <c r="D2" t="n" s="3">
         <v>0.0</v>
@@ -340,10 +340,10 @@
         <v>20</v>
       </c>
       <c r="C3" t="n" s="3">
-        <v>528500.0</v>
+        <v>0.0</v>
       </c>
       <c r="D3" t="n" s="3">
-        <v>2772000.0</v>
+        <v>0.0</v>
       </c>
     </row>
   </sheetData>

--- a/BaoCaoThongKe.xlsx
+++ b/BaoCaoThongKe.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
   <si>
     <t>CHỈ SỐ TỔNG QUAN HỆ THỐNG</t>
   </si>
@@ -61,6 +61,9 @@
     <t>THUONG_TRU</t>
   </si>
   <si>
+    <t>TAM_TRU</t>
+  </si>
+  <si>
     <t>STT</t>
   </si>
   <si>
@@ -79,13 +82,19 @@
     <t>Quỹ vì người nghèo năm 2023</t>
   </si>
   <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>fdf</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>Mốc thời gian</t>
   </si>
   <si>
     <t>Doanh thu (VND)</t>
-  </si>
-  <si>
-    <t>2023-10</t>
   </si>
 </sst>
 </file>
@@ -186,7 +195,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="33.80078125" customWidth="true" bestFit="true"/>
@@ -211,7 +220,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="5">
@@ -219,7 +228,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="6">
@@ -227,7 +236,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="n">
-        <v>728500.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="7">
@@ -256,7 +265,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n" s="2">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="13">
@@ -264,7 +273,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n" s="2">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="16">
@@ -285,7 +294,15 @@
         <v>14</v>
       </c>
       <c r="B18" t="n" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="B19" t="n" s="2">
+        <v>8.0</v>
       </c>
     </row>
   </sheetData>
@@ -295,7 +312,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="4.2734375" customWidth="true" bestFit="true"/>
@@ -306,16 +323,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2">
@@ -323,7 +340,7 @@
         <v>1.0</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" t="n" s="3">
         <v>0.0</v>
@@ -337,12 +354,54 @@
         <v>2.0</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" t="n" s="3">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="C4" t="n" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D4" t="n" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="C5" t="n" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D5" t="n" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="C6" t="n" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D6" t="n" s="3">
         <v>0.0</v>
       </c>
     </row>
@@ -353,7 +412,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="4.2734375" customWidth="true" bestFit="true"/>
@@ -363,24 +422,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="C2" t="n" s="3">
-        <v>728500.0</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
